--- a/sheets/민요/검수/풍년가 (채보1).xlsx
+++ b/sheets/민요/검수/풍년가 (채보1).xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4007,8 +4129,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4027,975 +4153,1005 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">풍년가 — 민요채보-1/풍년가.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">풍년가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="G4" s="17"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="17"/>
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="Q4" s="17"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="18"/>
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="18"/>
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="18"/>
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="18"/>
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="18"/>
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="O5" s="18"/>
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="Q5" s="18"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="16"/>
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M6" s="16"/>
+      <c r="N6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E7" s="17"/>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="19"/>
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="M7" s="17"/>
+      <c r="N7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="O7" s="17"/>
+      <c r="P7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q7" s="17"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 ‹</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="18"/>
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K8" s="18"/>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △
 ‹</t>
-        </is>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M8" s="18"/>
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="17"/>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="17"/>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="17"/>
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O10" s="17"/>
+      <c r="P10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="Q10" s="17"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="18"/>
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="18"/>
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="18"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="18"/>
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="18"/>
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="18"/>
+      <c r="P11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="G13" s="17"/>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K13" s="17"/>
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="17"/>
+      <c r="P13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" s="18"/>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="I14" s="18"/>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="M14" s="18"/>
+      <c r="N14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="O14" s="20"/>
+      <c r="P14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q14" s="2"/>
+      <c r="Q14" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/풍년가 (채보1).xlsx
+++ b/sheets/민요/검수/풍년가 (채보1).xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I29" s="2"/>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△|‹</t>
+          <t xml:space="preserve">–|△|‹</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △
 ‹</t>
         </is>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I87" s="2"/>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I95" s="2"/>
@@ -4085,12 +4085,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4301,7 +4301,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="10"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="L6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M6" s="8"/>
@@ -4445,7 +4445,7 @@
       <c r="E7" s="9"/>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4479,14 +4479,14 @@
       <c r="M7" s="9"/>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4541,7 +4541,7 @@
       <c r="K8" s="10"/>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △
 ‹</t>
         </is>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -4866,7 +4866,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
@@ -4890,13 +4890,13 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="9"/>
@@ -4929,7 +4929,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4960,7 +4960,7 @@
       <c r="I14" s="10"/>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/풍년가 (채보1).xlsx
+++ b/sheets/민요/검수/풍년가 (채보1).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4130,105 +4168,105 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">풍년가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4236,190 +4274,190 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="G4" s="23"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="23"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="24"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="24"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="24"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="24"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="24"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="24"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="24"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
+      <c r="Q5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4427,142 +4465,142 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="26"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="23"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="23"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 ‹</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="24"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="24"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △
 ‹</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="24"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4570,82 +4608,82 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4653,210 +4691,210 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="23"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="23"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="23"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="23"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="23"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
+      <c r="Q10" s="23"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="24"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="24"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="24"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M11" s="24"/>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="O11" s="24"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q11" s="10"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4864,127 +4902,127 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="23"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="23"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="24"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="24"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="24"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="24"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="M14" s="24"/>
+      <c r="N14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/풍년가 (채보1).xlsx
+++ b/sheets/민요/검수/풍년가 (채보1).xlsx
@@ -4145,28 +4145,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="23"/>
@@ -4324,18 +4324,18 @@
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4345,13 +4345,13 @@
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -4363,19 +4363,19 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="25" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="23"/>
@@ -4511,7 +4511,7 @@
       <c r="K7" s="26"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M7" s="23"/>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4958,12 +4958,12 @@
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -5019,7 +5019,7 @@
       <c r="O14" s="27"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="24"/>

--- a/sheets/민요/검수/풍년가 (채보1).xlsx
+++ b/sheets/민요/검수/풍년가 (채보1).xlsx
@@ -1665,14 +1665,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|△|‹</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -3436,13 +3435,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚|‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I78" s="2"/>
@@ -4166,7 +4164,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="82.06" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4189,7 +4187,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="82.06" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4272,7 +4270,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="82.06" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4335,7 +4333,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="82.06" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4386,7 +4384,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="82.06" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4463,7 +4461,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="82.06" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="25" t="inlineStr">
         <is>
@@ -4530,7 +4528,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="82.06" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4545,8 +4543,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E8" s="24"/>
@@ -4580,8 +4577,7 @@
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -4606,7 +4602,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="82.06" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4689,7 +4685,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="82.06" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4756,7 +4752,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="82.06" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4817,7 +4813,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="82.06" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4900,7 +4896,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="82.06" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4963,7 +4959,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="82.06" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/풍년가 (채보1).xlsx
+++ b/sheets/민요/검수/풍년가 (채보1).xlsx
@@ -2344,13 +2344,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -4994,8 +4993,7 @@
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="24"/>

--- a/sheets/민요/검수/풍년가 (채보1).xlsx
+++ b/sheets/민요/검수/풍년가 (채보1).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +238,21 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4193,7 +4213,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4203,7 +4223,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -4213,7 +4233,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
@@ -4223,7 +4243,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -4233,7 +4253,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4243,7 +4263,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -4253,7 +4273,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4263,7 +4283,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4276,7 +4296,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -4286,7 +4306,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4296,15 +4316,15 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="29"/>
       <c r="H4" s="21"/>
-      <c r="I4" s="23"/>
+      <c r="I4" s="29"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4314,7 +4334,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="M4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -4324,13 +4344,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="23"/>
+      <c r="O4" s="29"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q4" s="23"/>
+      <c r="Q4" s="29"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -4339,49 +4359,49 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="24"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="24"/>
+      <c r="G5" s="30"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="24"/>
+      <c r="I5" s="30"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="24"/>
+      <c r="K5" s="30"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="24"/>
+      <c r="M5" s="30"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="24"/>
+      <c r="O5" s="30"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="24"/>
+      <c r="Q5" s="30"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -4391,7 +4411,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
@@ -4401,13 +4421,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4417,7 +4437,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4428,7 +4448,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4438,13 +4458,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M6" s="22"/>
+      <c r="M6" s="28"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4454,7 +4474,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4467,7 +4487,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4477,14 +4497,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4495,7 +4515,7 @@
 南</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4505,27 +4525,27 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="26"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M7" s="23"/>
+      <c r="M7" s="29"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="29"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="Q7" s="23"/>
+      <c r="Q7" s="29"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -4535,7 +4555,7 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -4545,13 +4565,13 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E8" s="24"/>
+      <c r="E8" s="30"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4561,7 +4581,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4572,20 +4592,20 @@
 無</t>
         </is>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="30"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M8" s="24"/>
+      <c r="M8" s="30"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="O8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4595,7 +4615,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="24" t="inlineStr">
+      <c r="Q8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4608,7 +4628,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4618,7 +4638,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
@@ -4628,7 +4648,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -4638,7 +4658,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -4648,7 +4668,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4658,7 +4678,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -4668,7 +4688,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4678,7 +4698,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4692,14 +4712,14 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="23"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4710,28 +4730,28 @@
 姑</t>
         </is>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="29"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="23"/>
+      <c r="I10" s="29"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="29"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr">
+      <c r="M10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -4742,14 +4762,14 @@
 姑</t>
         </is>
       </c>
-      <c r="O10" s="23"/>
+      <c r="O10" s="29"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="23"/>
+      <c r="Q10" s="29"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -4759,21 +4779,21 @@
 姑</t>
         </is>
       </c>
-      <c r="C11" s="24"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="24"/>
+      <c r="E11" s="30"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4783,34 +4803,34 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="24"/>
+      <c r="I11" s="30"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="24"/>
+      <c r="K11" s="30"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="24"/>
+      <c r="M11" s="30"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="O11" s="24"/>
+      <c r="O11" s="30"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q11" s="24"/>
+      <c r="Q11" s="30"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -4819,7 +4839,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4829,7 +4849,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -4839,7 +4859,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -4849,7 +4869,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4859,7 +4879,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4869,7 +4889,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -4879,7 +4899,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4889,7 +4909,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4902,14 +4922,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4920,26 +4940,26 @@
 姑</t>
         </is>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="29"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="29"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="29"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
+      <c r="M13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -4950,13 +4970,13 @@
 姑</t>
         </is>
       </c>
-      <c r="O13" s="23"/>
+      <c r="O13" s="29"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="23"/>
+      <c r="Q13" s="29"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -4966,21 +4986,21 @@
 △</t>
         </is>
       </c>
-      <c r="C14" s="24"/>
+      <c r="C14" s="30"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="24"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="G14" s="27" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4990,33 +5010,33 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="24"/>
+      <c r="I14" s="30"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="24"/>
+      <c r="K14" s="30"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="24"/>
+      <c r="M14" s="30"/>
       <c r="N14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="24"/>
+      <c r="Q14" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/풍년가 (채보1).xlsx
+++ b/sheets/민요/검수/풍년가 (채보1).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,25 +227,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -313,11 +293,7 @@
           <t xml:space="preserve">쪽</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197</t>
-        </is>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -423,7 +399,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인쇄된 줄·정간 번호 있음</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 번호 1~8, 정간 번호 1~12, 굵은 선 3칸마다) → 3/4·12. 오른쪽부터 8줄 모두 사용, 왼쪽 빈 줄 1개 제외. 가사는 각 율명 줄 오른쪽 칸. 줄3·줄7 6정간 아래 경계에 &lt; 표시(‹). 줄2·줄6 12정간 아래 글자는 亻黃(僙)로 판독.</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1450,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙 확실치 않음</t>
+          <t xml:space="preserve">아래 글자 亻無처럼도 보임(僙?)</t>
         </is>
       </c>
       <c r="K25" s="2"/>
@@ -1648,18 +1624,22 @@
       <c r="F30" s="2">
         <v>2</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="4"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 –일 수도</t>
+        </is>
+      </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31">
@@ -2027,18 +2007,22 @@
       <c r="F40" s="2">
         <v>1</v>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="4"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 획(·일 수도), 줄8과 같게</t>
+        </is>
+      </c>
       <c r="K40" s="2"/>
     </row>
     <row r="41">
@@ -2102,22 +2086,18 @@
       <c r="F42" s="2">
         <v>2</v>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌 확실치 않음</t>
-        </is>
-      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="4"/>
       <c r="K42" s="2"/>
     </row>
     <row r="43">
@@ -3243,7 +3223,7 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙 확실치 않음</t>
+          <t xml:space="preserve">아래 글자 亻無처럼도 보임(僙?)</t>
         </is>
       </c>
       <c r="K72" s="2"/>
@@ -3454,12 +3434,13 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">–
+·</t>
         </is>
       </c>
       <c r="I78" s="2"/>
@@ -3870,26 +3851,22 @@
       <c r="F89" s="2">
         <v>2</v>
       </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I89" s="3" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌 확실치 않음</t>
-        </is>
-      </c>
+      <c r="J89" s="4"/>
       <c r="K89" s="2"/>
     </row>
     <row r="90">
@@ -4183,7 +4160,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4206,14 +4183,14 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4223,7 +4200,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -4233,7 +4210,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="28" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
@@ -4243,7 +4220,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -4253,7 +4230,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4263,7 +4240,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="28" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -4273,7 +4250,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="28" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4283,20 +4260,20 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="28" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -4306,7 +4283,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4316,15 +4293,15 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="29"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="21"/>
-      <c r="I4" s="29"/>
+      <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="29" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4334,7 +4311,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="29" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -4344,66 +4321,66 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="29"/>
+      <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q4" s="29"/>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
+      <c r="Q4" s="23"/>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="30"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="30"/>
+      <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="30"/>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="I5" s="24"/>
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="30"/>
+      <c r="K5" s="26"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="30"/>
+      <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="30"/>
+      <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q5" s="30"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+      <c r="Q5" s="24"/>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4411,7 +4388,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
@@ -4421,13 +4398,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4437,7 +4414,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4448,7 +4425,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4458,13 +4435,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M6" s="28"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O6" s="28" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
@@ -4474,20 +4451,20 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="28" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">년</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="55.19" customHeight="1">
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4497,14 +4474,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="29"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4515,39 +4492,39 @@
 南</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="K7" s="23"/>
+      <c r="L7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M7" s="29"/>
+      <c r="M7" s="27"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="O7" s="29"/>
+      <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="Q7" s="29"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
+      <c r="Q7" s="23"/>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4555,23 +4532,24 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E8" s="30"/>
+          <t xml:space="preserve">–
+–</t>
+        </is>
+      </c>
+      <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4581,7 +4559,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4592,20 +4570,20 @@
 無</t>
         </is>
       </c>
-      <c r="K8" s="30"/>
+      <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M8" s="30"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="30" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4615,20 +4593,20 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="30" t="inlineStr">
+      <c r="Q8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="55.19" customHeight="1">
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4638,7 +4616,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
@@ -4648,7 +4626,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -4658,7 +4636,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -4668,7 +4646,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4678,7 +4656,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="28" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -4688,7 +4666,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O9" s="28" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -4698,13 +4676,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="28" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="55.19" customHeight="1">
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4712,14 +4690,14 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="29"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4730,28 +4708,28 @@
 姑</t>
         </is>
       </c>
-      <c r="G10" s="29"/>
+      <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="29"/>
+      <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="29"/>
+      <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="29" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -4762,16 +4740,16 @@
 姑</t>
         </is>
       </c>
-      <c r="O10" s="29"/>
+      <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="29"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
+      <c r="Q10" s="23"/>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4779,21 +4757,21 @@
 姑</t>
         </is>
       </c>
-      <c r="C11" s="30"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="30"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G11" s="30" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4803,43 +4781,43 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="30"/>
+      <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="30"/>
+      <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="30"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="O11" s="30"/>
+      <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q11" s="30"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+      <c r="Q11" s="24"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4849,7 +4827,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -4859,7 +4837,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -4869,7 +4847,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4879,7 +4857,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="28" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4889,7 +4867,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="28" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -4899,7 +4877,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="28" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4909,27 +4887,27 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q12" s="28" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="55.19" customHeight="1">
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="29"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4940,26 +4918,26 @@
 姑</t>
         </is>
       </c>
-      <c r="G13" s="29"/>
+      <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="29"/>
+      <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="29"/>
+      <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M13" s="29" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -4970,15 +4948,15 @@
 姑</t>
         </is>
       </c>
-      <c r="O13" s="29"/>
+      <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="29"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+      <c r="Q13" s="23"/>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4986,21 +4964,21 @@
 △</t>
         </is>
       </c>
-      <c r="C14" s="30"/>
+      <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="30"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="G14" s="32" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5010,33 +4988,33 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="30"/>
+      <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="30"/>
+      <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="30"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="O14" s="32"/>
+      <c r="O14" s="26"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="30"/>
+      <c r="Q14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
